--- a/student_assessment_forms/023_joint_making_rules_assessment--student_assessment_forms.xlsx
+++ b/student_assessment_forms/023_joint_making_rules_assessment--student_assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -443,7 +443,7 @@
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="49" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -551,14 +551,10 @@
           <t>What type of joint are you creating?</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>What type of joint are you creating?</t>
-        </is>
-      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -578,14 +574,10 @@
           <t>What type of joint is the question referring to?</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>What type of joint is the question referring to?</t>
-        </is>
-      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -605,14 +597,10 @@
           <t>Which joint is being referred to in this question?</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Which joint is being referred to in this question?</t>
-        </is>
-      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -632,14 +620,10 @@
           <t>What is the confidence level of the selected joint?</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>What is the confidence level of the selected joint?</t>
-        </is>
-      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -659,14 +643,10 @@
           <t>Why is the joint important?</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Why is the joint important?</t>
-        </is>
-      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -686,14 +666,10 @@
           <t>What type of joint is not important?</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>What type of joint is not important?</t>
-        </is>
-      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -713,21 +689,17 @@
           <t>Why is this joint not important?</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Why is this joint not important?</t>
-        </is>
-      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -740,11 +712,7 @@
           <t>Additional Comments</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Additional Comments</t>
-        </is>
-      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -767,11 +735,7 @@
           <t>Written Explanation</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Written Explanation</t>
-        </is>
-      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -794,21 +758,17 @@
           <t>Written Answer</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Written Answer</t>
-        </is>
-      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -818,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Joint Making Rules Assessment</t>
+          <t>What is the date of completion?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -831,7 +791,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -841,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>What is the time of completion?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -864,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>What is the email address for contact information?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -877,7 +837,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -887,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>What is the label for this page?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -900,7 +860,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -910,13 +870,13 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>What is the number of joints being assessed?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -933,20 +893,20 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>What is the written answer for the joint assessment?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -956,20 +916,20 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>What is the date of the joint assessment?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -979,20 +939,20 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>What is the email address for the joint assessment?</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1002,20 +962,20 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>What is the written explanation for the joint assessment?</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1025,20 +985,20 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>What is the time of the joint assessment?</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1048,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>What is the text for the joint assessment?</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1061,46 +1021,46 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>joint_making_rules_assessment_form_questions_22</t>
+          <t>joint_making_rules_assessment_form_questions_23</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Joint Making Rules Assessment Form Questions 23</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>joint_making_rules_assessment_form_questions_23</t>
+          <t>joint_making_rules_assessment_form_questions_24</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Joint Making Rules Assessment Form Questions 24</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1112,18 +1072,18 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>joint_making_rules_assessment_form_questions_24</t>
+          <t>joint_making_rules_assessment_form_questions_25</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Joint Making Rules Assessment Form Questions 25</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1138,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1176,7 +1136,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>butt_joints</t>
+          <t>butt joints</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1153,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>dowel_joints</t>
+          <t>dowel joints</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1170,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>dado_joints</t>
+          <t>dado joints</t>
         </is>
       </c>
     </row>
@@ -1227,41 +1187,41 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>edge_joints</t>
+          <t>edge joints</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>joint_making_rules_assessment_form_questions_1_choices</t>
+          <t>joint_making_rules_assessment_form_questions_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>dado_joints</t>
+          <t>butt_joints</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>dado_joints</t>
+          <t>butt joints</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>joint_making_rules_assessment_form_questions_1_choices</t>
+          <t>joint_making_rules_assessment_form_questions_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>dowel_joints</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>dowel joints</t>
         </is>
       </c>
     </row>
@@ -1273,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>butt_joints</t>
+          <t>dado_joints</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>butt_joints</t>
+          <t>dado joints</t>
         </is>
       </c>
     </row>
@@ -1290,46 +1250,46 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>dowel_joints</t>
+          <t>edge_joints</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>dowel_joints</t>
+          <t>edge joints</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>joint_making_rules_assessment_form_questions_2_choices</t>
+          <t>joint_making_rules_assessment_form_questions_3_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>dado_joints</t>
+          <t>butt_joints</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>dado_joints</t>
+          <t>butt joints</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>joint_making_rules_assessment_form_questions_2_choices</t>
+          <t>joint_making_rules_assessment_form_questions_3_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>edge_joints</t>
+          <t>dowel_joints</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>edge_joints</t>
+          <t>dowel joints</t>
         </is>
       </c>
     </row>
@@ -1341,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>butt_joints</t>
+          <t>dado_joints</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>butt_joints</t>
+          <t>dado joints</t>
         </is>
       </c>
     </row>
@@ -1358,46 +1318,46 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>dowel_joints</t>
+          <t>edge_joints</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>dowel_joints</t>
+          <t>edge joints</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>joint_making_rules_assessment_form_questions_3_choices</t>
+          <t>joint_making_rules_assessment_form_questions_4_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>dado_joints</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>dado_joints</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>joint_making_rules_assessment_form_questions_3_choices</t>
+          <t>joint_making_rules_assessment_form_questions_4_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>edge_joints</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>edge_joints</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1409,46 +1369,46 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>joint_making_rules_assessment_form_questions_4_choices</t>
+          <t>joint_making_rules_assessment_form_questions_6_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>butt_joints</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>butt joints</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>joint_making_rules_assessment_form_questions_4_choices</t>
+          <t>joint_making_rules_assessment_form_questions_6_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>dowel_joints</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>dowel joints</t>
         </is>
       </c>
     </row>
@@ -1460,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>butt_joints</t>
+          <t>dado_joints</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>butt_joints</t>
+          <t>dado joints</t>
         </is>
       </c>
     </row>
@@ -1477,114 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>dowel_joints</t>
+          <t>edge_joints</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>dowel_joints</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>joint_making_rules_assessment_form_questions_6_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>dado_joints</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>dado_joints</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>joint_making_rules_assessment_form_questions_6_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>edge_joints</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>edge_joints</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>joint_making_rules_assessment_form_questions_18_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>joint_making_rules_assessment_form_questions_18_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>joint_making_rules_assessment_form_questions_19_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>joint_making_rules_assessment_form_questions_19_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>option2</t>
+          <t>edge joints</t>
         </is>
       </c>
     </row>
